--- a/research/traditional_assets/database/data/romania/romania_building_materials.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_building_materials.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.316</v>
+        <v>-0.299</v>
       </c>
       <c r="G2">
-        <v>-0.2161016949152542</v>
+        <v>-0.5208791208791208</v>
       </c>
       <c r="H2">
-        <v>-0.2161016949152542</v>
+        <v>-0.5208791208791208</v>
       </c>
       <c r="I2">
-        <v>-0.2584745762711865</v>
+        <v>-0.3802197802197802</v>
       </c>
       <c r="J2">
-        <v>-0.2584745762711865</v>
+        <v>-0.3740836684928904</v>
       </c>
       <c r="K2">
-        <v>-0.444</v>
+        <v>3.42</v>
       </c>
       <c r="L2">
-        <v>-0.6271186440677966</v>
+        <v>7.516483516483516</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.122</v>
+        <v>0.123</v>
       </c>
       <c r="V2">
-        <v>0.1900311526479751</v>
+        <v>0.1375838926174497</v>
       </c>
       <c r="W2">
-        <v>0.2596491228070176</v>
+        <v>-1.628571428571429</v>
       </c>
       <c r="X2">
-        <v>0.615745106595384</v>
+        <v>0.1503465062058406</v>
       </c>
       <c r="Y2">
-        <v>-0.3560959837883664</v>
+        <v>-1.778917934777269</v>
       </c>
       <c r="Z2">
-        <v>0.1654978962131837</v>
+        <v>0.1118485742379548</v>
       </c>
       <c r="AA2">
-        <v>-0.04277699859747545</v>
+        <v>-0.04184072496663351</v>
       </c>
       <c r="AB2">
-        <v>0.08909701396558978</v>
+        <v>0.138576820470701</v>
       </c>
       <c r="AC2">
-        <v>-0.1318740125630652</v>
+        <v>-0.1804175454373345</v>
       </c>
       <c r="AD2">
-        <v>6.29</v>
+        <v>0.158</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.29</v>
+        <v>0.158</v>
       </c>
       <c r="AG2">
-        <v>6.168</v>
+        <v>0.035</v>
       </c>
       <c r="AH2">
-        <v>0.9073860357761108</v>
+        <v>0.1501901140684411</v>
       </c>
       <c r="AI2">
-        <v>1.501193317422435</v>
+        <v>0.08787541713014461</v>
       </c>
       <c r="AJ2">
-        <v>0.905726872246696</v>
+        <v>0.03767491926803014</v>
       </c>
       <c r="AK2">
-        <v>1.516224188790561</v>
+        <v>0.02089552238805971</v>
       </c>
       <c r="AL2">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.074</v>
+        <v>-0.106</v>
       </c>
       <c r="AN2">
-        <v>-78.625</v>
-      </c>
-      <c r="AO2">
-        <v>-2.316455696202532</v>
+        <v>-3.590909090909091</v>
       </c>
       <c r="AP2">
-        <v>-77.09999999999999</v>
+        <v>-0.7954545454545455</v>
       </c>
       <c r="AQ2">
-        <v>-2.472972972972973</v>
+        <v>1.632075471698113</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.316</v>
+        <v>-0.299</v>
       </c>
       <c r="G3">
-        <v>-0.2161016949152542</v>
+        <v>-0.5208791208791208</v>
       </c>
       <c r="H3">
-        <v>-0.2161016949152542</v>
+        <v>-0.5208791208791208</v>
       </c>
       <c r="I3">
-        <v>-0.2584745762711865</v>
+        <v>-0.3802197802197802</v>
       </c>
       <c r="J3">
-        <v>-0.2584745762711865</v>
+        <v>-0.3740836684928904</v>
       </c>
       <c r="K3">
-        <v>-0.444</v>
+        <v>3.42</v>
       </c>
       <c r="L3">
-        <v>-0.6271186440677966</v>
+        <v>7.516483516483516</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +749,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.122</v>
+        <v>0.123</v>
       </c>
       <c r="V3">
-        <v>0.1900311526479751</v>
+        <v>0.1375838926174497</v>
       </c>
       <c r="W3">
-        <v>0.2596491228070176</v>
+        <v>-1.628571428571429</v>
       </c>
       <c r="X3">
-        <v>0.615745106595384</v>
+        <v>0.1503465062058406</v>
       </c>
       <c r="Y3">
-        <v>-0.3560959837883664</v>
+        <v>-1.778917934777269</v>
       </c>
       <c r="Z3">
-        <v>0.1654978962131837</v>
+        <v>0.1118485742379548</v>
       </c>
       <c r="AA3">
-        <v>-0.04277699859747545</v>
+        <v>-0.04184072496663351</v>
       </c>
       <c r="AB3">
-        <v>0.08909701396558978</v>
+        <v>0.138576820470701</v>
       </c>
       <c r="AC3">
-        <v>-0.1318740125630652</v>
+        <v>-0.1804175454373345</v>
       </c>
       <c r="AD3">
-        <v>6.29</v>
+        <v>0.158</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.29</v>
+        <v>0.158</v>
       </c>
       <c r="AG3">
-        <v>6.168</v>
+        <v>0.035</v>
       </c>
       <c r="AH3">
-        <v>0.9073860357761108</v>
+        <v>0.1501901140684411</v>
       </c>
       <c r="AI3">
-        <v>1.501193317422435</v>
+        <v>0.08787541713014461</v>
       </c>
       <c r="AJ3">
-        <v>0.905726872246696</v>
+        <v>0.03767491926803014</v>
       </c>
       <c r="AK3">
-        <v>1.516224188790561</v>
+        <v>0.02089552238805971</v>
       </c>
       <c r="AL3">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.074</v>
+        <v>-0.106</v>
       </c>
       <c r="AN3">
-        <v>-78.625</v>
-      </c>
-      <c r="AO3">
-        <v>-2.316455696202532</v>
+        <v>-3.590909090909091</v>
       </c>
       <c r="AP3">
-        <v>-77.09999999999999</v>
+        <v>-0.7954545454545455</v>
       </c>
       <c r="AQ3">
-        <v>-2.472972972972973</v>
+        <v>1.632075471698113</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_building_materials.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_building_materials.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.299</v>
+        <v>-0.27</v>
       </c>
       <c r="G2">
-        <v>-0.5208791208791208</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="H2">
-        <v>-0.5208791208791208</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="I2">
-        <v>-0.3802197802197802</v>
+        <v>-0.3964646464646465</v>
       </c>
       <c r="J2">
-        <v>-0.3740836684928904</v>
+        <v>-0.3964646464646465</v>
       </c>
       <c r="K2">
-        <v>3.42</v>
+        <v>-0.113</v>
       </c>
       <c r="L2">
-        <v>7.516483516483516</v>
+        <v>-0.2853535353535354</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +624,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.123</v>
+        <v>1.58</v>
       </c>
       <c r="V2">
-        <v>0.1375838926174497</v>
+        <v>1.519230769230769</v>
       </c>
       <c r="W2">
-        <v>-1.628571428571429</v>
+        <v>-0.06890243902439025</v>
       </c>
       <c r="X2">
-        <v>0.1503465062058406</v>
+        <v>0.110740422128467</v>
       </c>
       <c r="Y2">
-        <v>-1.778917934777269</v>
+        <v>-0.1796428611528572</v>
       </c>
       <c r="Z2">
-        <v>0.1118485742379548</v>
+        <v>0.2364179104477612</v>
       </c>
       <c r="AA2">
-        <v>-0.04184072496663351</v>
+        <v>-0.0937313432835821</v>
       </c>
       <c r="AB2">
-        <v>0.138576820470701</v>
+        <v>0.110740422128467</v>
       </c>
       <c r="AC2">
-        <v>-0.1804175454373345</v>
+        <v>-0.2044717654120491</v>
       </c>
       <c r="AD2">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.035</v>
+        <v>-1.58</v>
       </c>
       <c r="AH2">
-        <v>0.1501901140684411</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.08787541713014461</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.03767491926803014</v>
+        <v>2.925925925925926</v>
       </c>
       <c r="AK2">
-        <v>0.02089552238805971</v>
+        <v>-22.57142857142862</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.106</v>
+        <v>-0.065</v>
       </c>
       <c r="AN2">
-        <v>-3.590909090909091</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-0.7954545454545455</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="AQ2">
-        <v>1.632075471698113</v>
+        <v>2.415384615384615</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.299</v>
+        <v>-0.27</v>
       </c>
       <c r="G3">
-        <v>-0.5208791208791208</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="H3">
-        <v>-0.5208791208791208</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="I3">
-        <v>-0.3802197802197802</v>
+        <v>-0.3964646464646465</v>
       </c>
       <c r="J3">
-        <v>-0.3740836684928904</v>
+        <v>-0.3964646464646465</v>
       </c>
       <c r="K3">
-        <v>3.42</v>
+        <v>-0.113</v>
       </c>
       <c r="L3">
-        <v>7.516483516483516</v>
+        <v>-0.2853535353535354</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +749,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1.58</v>
+      </c>
+      <c r="V3">
+        <v>1.519230769230769</v>
+      </c>
+      <c r="W3">
+        <v>-0.06890243902439025</v>
+      </c>
+      <c r="X3">
+        <v>0.110740422128467</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1796428611528572</v>
+      </c>
+      <c r="Z3">
+        <v>0.2364179104477612</v>
+      </c>
+      <c r="AA3">
+        <v>-0.0937313432835821</v>
+      </c>
+      <c r="AB3">
+        <v>0.110740422128467</v>
+      </c>
+      <c r="AC3">
+        <v>-0.2044717654120491</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-1.58</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>2.925925925925926</v>
+      </c>
+      <c r="AK3">
+        <v>-22.57142857142862</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-0.065</v>
+      </c>
+      <c r="AN3">
         <v>-0</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.123</v>
-      </c>
-      <c r="V3">
-        <v>0.1375838926174497</v>
-      </c>
-      <c r="W3">
-        <v>-1.628571428571429</v>
-      </c>
-      <c r="X3">
-        <v>0.1503465062058406</v>
-      </c>
-      <c r="Y3">
-        <v>-1.778917934777269</v>
-      </c>
-      <c r="Z3">
-        <v>0.1118485742379548</v>
-      </c>
-      <c r="AA3">
-        <v>-0.04184072496663351</v>
-      </c>
-      <c r="AB3">
-        <v>0.138576820470701</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1804175454373345</v>
-      </c>
-      <c r="AD3">
-        <v>0.158</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.158</v>
-      </c>
-      <c r="AG3">
-        <v>0.035</v>
-      </c>
-      <c r="AH3">
-        <v>0.1501901140684411</v>
-      </c>
-      <c r="AI3">
-        <v>0.08787541713014461</v>
-      </c>
-      <c r="AJ3">
-        <v>0.03767491926803014</v>
-      </c>
-      <c r="AK3">
-        <v>0.02089552238805971</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-0.106</v>
-      </c>
-      <c r="AN3">
-        <v>-3.590909090909091</v>
-      </c>
       <c r="AP3">
-        <v>-0.7954545454545455</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="AQ3">
-        <v>1.632075471698113</v>
+        <v>2.415384615384615</v>
       </c>
     </row>
   </sheetData>
